--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N13_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N13_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>22.34835399942726</v>
+        <v>3.631607524906929</v>
       </c>
       <c r="D2" t="n">
-        <v>22.30193849854868</v>
+        <v>3.624065006014161</v>
       </c>
       <c r="E2" t="n">
-        <v>10.30293253904399</v>
+        <v>1.674226537594648</v>
       </c>
       <c r="F2" t="n">
-        <v>10.26767642685847</v>
+        <v>1.668497419364502</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1.161891532255186</v>
+        <v>0.1888073739914677</v>
       </c>
       <c r="D3" t="n">
-        <v>1.138182848867011</v>
+        <v>0.1849547129408894</v>
       </c>
       <c r="E3" t="n">
-        <v>10.30293253904399</v>
+        <v>1.674226537594648</v>
       </c>
       <c r="F3" t="n">
-        <v>10.26767642685847</v>
+        <v>1.668497419364502</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.97173914509391</v>
+        <v>3.407907611077761</v>
       </c>
       <c r="D4" t="n">
-        <v>21.00869881228815</v>
+        <v>3.413913556996824</v>
       </c>
       <c r="E4" t="n">
-        <v>10.30293253904399</v>
+        <v>1.674226537594648</v>
       </c>
       <c r="F4" t="n">
-        <v>10.26767642685847</v>
+        <v>1.668497419364502</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.68773980324563</v>
+        <v>4.336757718027416</v>
       </c>
       <c r="D5" t="n">
-        <v>26.7231058760132</v>
+        <v>4.342504704852145</v>
       </c>
       <c r="E5" t="n">
-        <v>10.30293253904399</v>
+        <v>1.674226537594648</v>
       </c>
       <c r="F5" t="n">
-        <v>10.26767642685847</v>
+        <v>1.668497419364502</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.36372255045249</v>
+        <v>3.471604914448529</v>
       </c>
       <c r="D6" t="n">
-        <v>21.38656212660869</v>
+        <v>3.475316345573913</v>
       </c>
       <c r="E6" t="n">
-        <v>10.30293253904399</v>
+        <v>1.674226537594648</v>
       </c>
       <c r="F6" t="n">
-        <v>10.26767642685847</v>
+        <v>1.668497419364502</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.83640822888957</v>
+        <v>4.360916337194555</v>
       </c>
       <c r="D7" t="n">
-        <v>26.82829215668979</v>
+        <v>4.359597475462092</v>
       </c>
       <c r="E7" t="n">
-        <v>10.30293253904399</v>
+        <v>1.674226537594648</v>
       </c>
       <c r="F7" t="n">
-        <v>10.26767642685847</v>
+        <v>1.668497419364502</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>25.76708468810412</v>
+        <v>4.187151261816919</v>
       </c>
       <c r="D8" t="n">
-        <v>25.73624761748398</v>
+        <v>4.182140237841147</v>
       </c>
       <c r="E8" t="n">
-        <v>10.30293253904399</v>
+        <v>1.674226537594648</v>
       </c>
       <c r="F8" t="n">
-        <v>10.26767642685847</v>
+        <v>1.668497419364502</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>11.25574972795167</v>
+        <v>1.829059330792146</v>
       </c>
       <c r="D9" t="n">
-        <v>11.29145532429857</v>
+        <v>1.834861490198517</v>
       </c>
       <c r="E9" t="n">
-        <v>10.30293253904399</v>
+        <v>1.674226537594648</v>
       </c>
       <c r="F9" t="n">
-        <v>10.26767642685847</v>
+        <v>1.668497419364502</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>47.20448229547186</v>
+        <v>7.670728373014176</v>
       </c>
       <c r="D10" t="n">
-        <v>46.58510611992124</v>
+        <v>7.570079744487201</v>
       </c>
       <c r="E10" t="n">
-        <v>10.30293253904399</v>
+        <v>1.674226537594648</v>
       </c>
       <c r="F10" t="n">
-        <v>10.26767642685847</v>
+        <v>1.668497419364502</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.14664094408293</v>
+        <v>5.223829153413476</v>
       </c>
       <c r="D11" t="n">
-        <v>31.48476528966409</v>
+        <v>5.116274359570415</v>
       </c>
       <c r="E11" t="n">
-        <v>10.30293253904399</v>
+        <v>1.674226537594648</v>
       </c>
       <c r="F11" t="n">
-        <v>10.26767642685847</v>
+        <v>1.668497419364502</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>24.51281670111996</v>
+        <v>3.983332713931994</v>
       </c>
       <c r="D12" t="n">
-        <v>24.50514488138299</v>
+        <v>3.982086043224736</v>
       </c>
       <c r="E12" t="n">
-        <v>10.30293253904399</v>
+        <v>1.674226537594648</v>
       </c>
       <c r="F12" t="n">
-        <v>10.26767642685847</v>
+        <v>1.668497419364502</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>25.47730423142769</v>
+        <v>4.140061937606999</v>
       </c>
       <c r="D13" t="n">
-        <v>26.99269469689228</v>
+        <v>4.386312888244996</v>
       </c>
       <c r="E13" t="n">
-        <v>10.30293253904399</v>
+        <v>1.674226537594648</v>
       </c>
       <c r="F13" t="n">
-        <v>10.26767642685847</v>
+        <v>1.668497419364502</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>24.91965140595502</v>
+        <v>4.049443353467691</v>
       </c>
       <c r="D14" t="n">
-        <v>24.13079116679608</v>
+        <v>3.921253564604364</v>
       </c>
       <c r="E14" t="n">
-        <v>10.30293253904399</v>
+        <v>1.674226537594648</v>
       </c>
       <c r="F14" t="n">
-        <v>10.26767642685847</v>
+        <v>1.668497419364502</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>16.81974547009177</v>
+        <v>2.733208638889913</v>
       </c>
       <c r="D15" t="n">
-        <v>16.08633066178084</v>
+        <v>2.614028732539386</v>
       </c>
       <c r="E15" t="n">
-        <v>10.30293253904399</v>
+        <v>1.674226537594648</v>
       </c>
       <c r="F15" t="n">
-        <v>10.26767642685847</v>
+        <v>1.668497419364502</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>4.112662231809294</v>
+        <v>0.6683076126690103</v>
       </c>
       <c r="D16" t="n">
-        <v>3.439893053050097</v>
+        <v>0.5589826211206408</v>
       </c>
       <c r="E16" t="n">
-        <v>10.30293253904399</v>
+        <v>1.674226537594648</v>
       </c>
       <c r="F16" t="n">
-        <v>10.26767642685847</v>
+        <v>1.668497419364502</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>18.60516823408055</v>
+        <v>3.02333983803809</v>
       </c>
       <c r="D17" t="n">
-        <v>18.29817950830239</v>
+        <v>2.973454170099138</v>
       </c>
       <c r="E17" t="n">
-        <v>10.30293253904399</v>
+        <v>1.674226537594648</v>
       </c>
       <c r="F17" t="n">
-        <v>10.26767642685847</v>
+        <v>1.668497419364502</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>13.23281617684355</v>
+        <v>2.150332628737078</v>
       </c>
       <c r="D18" t="n">
-        <v>13.82467545041248</v>
+        <v>2.246509760692029</v>
       </c>
       <c r="E18" t="n">
-        <v>10.30293253904399</v>
+        <v>1.674226537594648</v>
       </c>
       <c r="F18" t="n">
-        <v>10.26767642685847</v>
+        <v>1.668497419364502</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
